--- a/tools/content-pipeline/tests/fixtures/ioc_sample.xlsx
+++ b/tools/content-pipeline/tests/fixtures/ioc_sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="14.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,168 +413,418 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SP; Extinct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>English name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Counters</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Scientific Name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Breeding Range</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Nonbreeding Range</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>INFRACLASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASSERIFORMES</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NEOAVES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ORDER</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ORDER PASSERIFORMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>FamilyEN</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Scientific name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>English name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Passeriformes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tits</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Family Paridae</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Genus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Parus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Great Tit</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Paridae</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tits</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Parus major</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ssp</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Great Tit</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Passeriformes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Parus major major</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Genus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cyanistes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eurasian Blue Tit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Paridae</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tits</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Cyanistes caeruleus</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Eurasian Blue Tit</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Passeriformes</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Thrushes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Family Turdidae</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Genus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Turdus</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Common Blackbird</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Turdidae</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Thrushes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Turdus merula</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Common Blackbird</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Anseriformes</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ORDER</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ORDER ANSERIFORMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ducks, Geese, Swans</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Family Anatidae</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Genus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Cygnus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mute Swan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Anatidae</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ducks Geese and Swans</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Cygnus olor</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Mute Swan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Falconiformes</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ORDER</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ORDER FALCONIFORMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Falcons, Caracaras</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Family Falconidae</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Genus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Falco</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Common Kestrel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Falconidae</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Falcons</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Falco tinnunculus</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Common Kestrel</t>
         </is>
       </c>
     </row>
